--- a/src/test/resources/Bulk Excel File/SpecialTimerProduct/Test.xlsx
+++ b/src/test/resources/Bulk Excel File/SpecialTimerProduct/Test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\ZlaataQAseverRegression\src\test\resources\Bulk Excel File\SpecialTimerProduct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8BD9DF7-F869-4ECA-A4D1-94BADF849912}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD12FE49-67BD-4BAF-AC9A-2FFFEAEEDEE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>sku</t>
   </si>
@@ -33,10 +33,13 @@
     <t>discount</t>
   </si>
   <si>
-    <t>RW4</t>
+    <t>ZL14x4-BK-BK</t>
   </si>
   <si>
-    <t>RW3</t>
+    <t>ZL144-BK-GN</t>
+  </si>
+  <si>
+    <t>3Vi32-BK</t>
   </si>
 </sst>
 </file>
@@ -401,6 +404,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="7.19921875" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="12.8984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
@@ -410,9 +416,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="31.2">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>500</v>
@@ -420,15 +426,19 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
         <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>700</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
